--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831876</v>
+        <v>125831888</v>
       </c>
       <c r="B4" t="n">
-        <v>5479</v>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768216</v>
+        <v>768148</v>
       </c>
       <c r="R4" t="n">
-        <v>7244197</v>
+        <v>7243853</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -967,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831888</v>
+        <v>125831896</v>
       </c>
       <c r="B5" t="n">
         <v>78967</v>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768148</v>
+        <v>768175</v>
       </c>
       <c r="R5" t="n">
-        <v>7243853</v>
+        <v>7244238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831896</v>
+        <v>125831876</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>5479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768175</v>
+        <v>768216</v>
       </c>
       <c r="R6" t="n">
-        <v>7244238</v>
+        <v>7244197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831889</v>
+        <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>91380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768182</v>
+        <v>768186</v>
       </c>
       <c r="R30" t="n">
-        <v>7243990</v>
+        <v>7244183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831880</v>
+        <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91380</v>
+        <v>91238</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768186</v>
+        <v>768188</v>
       </c>
       <c r="R31" t="n">
-        <v>7244183</v>
+        <v>7244214</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831881</v>
+        <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>91238</v>
+        <v>78967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,21 +3655,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768188</v>
+        <v>768182</v>
       </c>
       <c r="R32" t="n">
-        <v>7244214</v>
+        <v>7243990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831898</v>
+        <v>125831868</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768185</v>
+        <v>768122</v>
       </c>
       <c r="R33" t="n">
-        <v>7244244</v>
+        <v>7243923</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831887</v>
+        <v>125831898</v>
       </c>
       <c r="B34" t="n">
         <v>78967</v>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768147</v>
+        <v>768185</v>
       </c>
       <c r="R34" t="n">
-        <v>7244072</v>
+        <v>7244244</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831868</v>
+        <v>125831887</v>
       </c>
       <c r="B35" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768122</v>
+        <v>768147</v>
       </c>
       <c r="R35" t="n">
-        <v>7243923</v>
+        <v>7244072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831897</v>
+        <v>125831867</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768187</v>
+        <v>768108</v>
       </c>
       <c r="R7" t="n">
-        <v>7244255</v>
+        <v>7243943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831883</v>
+        <v>125831897</v>
       </c>
       <c r="B8" t="n">
         <v>78967</v>
@@ -1287,23 +1287,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768238</v>
+        <v>768187</v>
       </c>
       <c r="R8" t="n">
-        <v>7244188</v>
+        <v>7244255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,18 +1331,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1368,10 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831867</v>
+        <v>125831883</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1366,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768108</v>
+        <v>768238</v>
       </c>
       <c r="R9" t="n">
-        <v>7243943</v>
+        <v>7244188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,12 +1435,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831866</v>
+        <v>125831873</v>
       </c>
       <c r="B11" t="n">
-        <v>57811</v>
+        <v>92707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768107</v>
+        <v>768223</v>
       </c>
       <c r="R11" t="n">
-        <v>7244257</v>
+        <v>7244174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831873</v>
+        <v>125831866</v>
       </c>
       <c r="B12" t="n">
-        <v>92700</v>
+        <v>57811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768223</v>
+        <v>768107</v>
       </c>
       <c r="R12" t="n">
-        <v>7244174</v>
+        <v>7244257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
         <v>125831857</v>
       </c>
       <c r="B14" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831863</v>
+        <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>57811</v>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,42 +2059,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768181</v>
+        <v>768160</v>
       </c>
       <c r="R16" t="n">
-        <v>7244196</v>
+        <v>7244178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2127,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,7 +2145,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831886</v>
+        <v>125831902</v>
       </c>
       <c r="B17" t="n">
         <v>78967</v>
@@ -2193,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768160</v>
+        <v>768129</v>
       </c>
       <c r="R17" t="n">
-        <v>7244178</v>
+        <v>7244186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831902</v>
+        <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,34 +2253,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768129</v>
+        <v>768181</v>
       </c>
       <c r="R18" t="n">
-        <v>7244186</v>
+        <v>7244196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2326,6 +2321,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,45 +2656,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831891</v>
+        <v>125831862</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768218</v>
+        <v>768217</v>
       </c>
       <c r="R22" t="n">
-        <v>7244090</v>
+        <v>7244177</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,6 +2731,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2753,32 +2762,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831899</v>
+        <v>125831878</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>58291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103042</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2788,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768171</v>
+        <v>768177</v>
       </c>
       <c r="R23" t="n">
-        <v>7244251</v>
+        <v>7244173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,49 +2859,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831862</v>
+        <v>125831891</v>
       </c>
       <c r="B24" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768217</v>
+        <v>768218</v>
       </c>
       <c r="R24" t="n">
-        <v>7244177</v>
+        <v>7244090</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2930,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831878</v>
+        <v>125831899</v>
       </c>
       <c r="B25" t="n">
-        <v>58291</v>
+        <v>78967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103042</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768177</v>
+        <v>768171</v>
       </c>
       <c r="R25" t="n">
-        <v>7244173</v>
+        <v>7244251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,49 +3053,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831861</v>
+        <v>125831851</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>78999</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768249</v>
+        <v>768168</v>
       </c>
       <c r="R26" t="n">
-        <v>7244155</v>
+        <v>7244250</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,11 +3124,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3162,7 +3153,7 @@
         <v>125831879</v>
       </c>
       <c r="B27" t="n">
-        <v>91234</v>
+        <v>91241</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,45 +3247,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831851</v>
+        <v>125831861</v>
       </c>
       <c r="B28" t="n">
-        <v>78999</v>
+        <v>56843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768168</v>
+        <v>768249</v>
       </c>
       <c r="R28" t="n">
-        <v>7244250</v>
+        <v>7244155</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,6 +3322,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831880</v>
+        <v>125831881</v>
       </c>
       <c r="B30" t="n">
-        <v>91380</v>
+        <v>91245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768186</v>
+        <v>768188</v>
       </c>
       <c r="R30" t="n">
-        <v>7244183</v>
+        <v>7244214</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831881</v>
+        <v>125831889</v>
       </c>
       <c r="B31" t="n">
-        <v>91238</v>
+        <v>78967</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768188</v>
+        <v>768182</v>
       </c>
       <c r="R31" t="n">
-        <v>7244214</v>
+        <v>7243990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,32 +3644,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831889</v>
+        <v>125831880</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>91387</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768182</v>
+        <v>768186</v>
       </c>
       <c r="R32" t="n">
-        <v>7243990</v>
+        <v>7244183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4132,7 +4132,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,10 +4429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125831894</v>
+        <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4440,21 +4440,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768196</v>
+        <v>768184</v>
       </c>
       <c r="R40" t="n">
-        <v>7244226</v>
+        <v>7244205</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125831850</v>
+        <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4537,21 +4537,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>768184</v>
+        <v>768196</v>
       </c>
       <c r="R41" t="n">
-        <v>7244205</v>
+        <v>7244226</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831853</v>
+        <v>125831888</v>
       </c>
       <c r="B3" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768115</v>
+        <v>768148</v>
       </c>
       <c r="R3" t="n">
-        <v>7244249</v>
+        <v>7243853</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831888</v>
+        <v>125831896</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768148</v>
+        <v>768175</v>
       </c>
       <c r="R4" t="n">
-        <v>7243853</v>
+        <v>7244238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831896</v>
+        <v>125831876</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>5479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768175</v>
+        <v>768216</v>
       </c>
       <c r="R5" t="n">
-        <v>7244238</v>
+        <v>7244197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1063,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831876</v>
+        <v>125831853</v>
       </c>
       <c r="B6" t="n">
-        <v>5479</v>
+        <v>78999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768216</v>
+        <v>768115</v>
       </c>
       <c r="R6" t="n">
-        <v>7244197</v>
+        <v>7244249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1143,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831873</v>
+        <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>92707</v>
+        <v>57811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768223</v>
+        <v>768107</v>
       </c>
       <c r="R11" t="n">
-        <v>7244174</v>
+        <v>7244257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831866</v>
+        <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>57811</v>
+        <v>92707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768107</v>
+        <v>768223</v>
       </c>
       <c r="R12" t="n">
-        <v>7244257</v>
+        <v>7244174</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831851</v>
+        <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768168</v>
+        <v>768193</v>
       </c>
       <c r="R26" t="n">
-        <v>7244250</v>
+        <v>7244227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831879</v>
+        <v>125831851</v>
       </c>
       <c r="B27" t="n">
-        <v>91241</v>
+        <v>78999</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768140</v>
+        <v>768168</v>
       </c>
       <c r="R27" t="n">
-        <v>7243836</v>
+        <v>7244250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3247,49 +3247,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831861</v>
+        <v>125831879</v>
       </c>
       <c r="B28" t="n">
-        <v>56843</v>
+        <v>91241</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768249</v>
+        <v>768140</v>
       </c>
       <c r="R28" t="n">
-        <v>7244155</v>
+        <v>7243836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,11 +3318,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3353,45 +3344,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831895</v>
+        <v>125831861</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768193</v>
+        <v>768249</v>
       </c>
       <c r="R29" t="n">
-        <v>7244227</v>
+        <v>7244155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,6 +3419,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831868</v>
+        <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768122</v>
+        <v>768185</v>
       </c>
       <c r="R33" t="n">
-        <v>7243923</v>
+        <v>7244244</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831898</v>
+        <v>125831887</v>
       </c>
       <c r="B34" t="n">
         <v>78967</v>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768185</v>
+        <v>768147</v>
       </c>
       <c r="R34" t="n">
-        <v>7244244</v>
+        <v>7244072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831887</v>
+        <v>125831864</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>57811</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768147</v>
+        <v>768102</v>
       </c>
       <c r="R35" t="n">
-        <v>7244072</v>
+        <v>7244258</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831864</v>
+        <v>125831868</v>
       </c>
       <c r="B36" t="n">
-        <v>57811</v>
+        <v>57648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768102</v>
+        <v>768122</v>
       </c>
       <c r="R36" t="n">
-        <v>7244258</v>
+        <v>7243923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4429,10 +4429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125831850</v>
+        <v>125831894</v>
       </c>
       <c r="B40" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4440,21 +4440,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768184</v>
+        <v>768196</v>
       </c>
       <c r="R40" t="n">
-        <v>7244205</v>
+        <v>7244226</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125831894</v>
+        <v>125831850</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4537,21 +4537,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>768196</v>
+        <v>768184</v>
       </c>
       <c r="R41" t="n">
-        <v>7244226</v>
+        <v>7244205</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125831888</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125831896</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>125831853</v>
       </c>
       <c r="B6" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831867</v>
+        <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>57648</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768108</v>
+        <v>768187</v>
       </c>
       <c r="R7" t="n">
-        <v>7243943</v>
+        <v>7244255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831897</v>
+        <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,16 +1287,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768187</v>
+        <v>768238</v>
       </c>
       <c r="R8" t="n">
-        <v>7244255</v>
+        <v>7244188</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1331,12 +1338,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831883</v>
+        <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1366,41 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768238</v>
+        <v>768108</v>
       </c>
       <c r="R9" t="n">
-        <v>7244188</v>
+        <v>7243943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,18 +1441,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831885</v>
+        <v>125831866</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>57811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768166</v>
+        <v>768107</v>
       </c>
       <c r="R10" t="n">
-        <v>7244249</v>
+        <v>7244257</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1544,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1563,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831866</v>
+        <v>125831885</v>
       </c>
       <c r="B11" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768107</v>
+        <v>768166</v>
       </c>
       <c r="R11" t="n">
-        <v>7244257</v>
+        <v>7244249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1642,6 +1641,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>125831871</v>
       </c>
       <c r="B13" t="n">
-        <v>78991</v>
+        <v>78992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>125831857</v>
       </c>
       <c r="B14" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831852</v>
+        <v>125831886</v>
       </c>
       <c r="B15" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768152</v>
+        <v>768160</v>
       </c>
       <c r="R15" t="n">
-        <v>7244247</v>
+        <v>7244178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831886</v>
+        <v>125831902</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768160</v>
+        <v>768129</v>
       </c>
       <c r="R16" t="n">
-        <v>7244178</v>
+        <v>7244186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831902</v>
+        <v>125831852</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768129</v>
+        <v>768152</v>
       </c>
       <c r="R17" t="n">
-        <v>7244186</v>
+        <v>7244247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
         <v>125831900</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>125831890</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,32 +2762,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831878</v>
+        <v>125831891</v>
       </c>
       <c r="B23" t="n">
-        <v>58291</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768177</v>
+        <v>768218</v>
       </c>
       <c r="R23" t="n">
-        <v>7244173</v>
+        <v>7244090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831891</v>
+        <v>125831899</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768218</v>
+        <v>768171</v>
       </c>
       <c r="R24" t="n">
-        <v>7244090</v>
+        <v>7244251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2956,32 +2956,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831899</v>
+        <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>58292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103042</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768171</v>
+        <v>768177</v>
       </c>
       <c r="R25" t="n">
-        <v>7244251</v>
+        <v>7244173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3056,7 +3056,7 @@
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,45 +3150,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831851</v>
+        <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>78999</v>
+        <v>56843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768168</v>
+        <v>768249</v>
       </c>
       <c r="R27" t="n">
-        <v>7244250</v>
+        <v>7244155</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,6 +3225,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3247,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831879</v>
+        <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>91241</v>
+        <v>79000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3258,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3282,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768140</v>
+        <v>768168</v>
       </c>
       <c r="R28" t="n">
-        <v>7243836</v>
+        <v>7244250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,49 +3353,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831861</v>
+        <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>56843</v>
+        <v>91242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768249</v>
+        <v>768140</v>
       </c>
       <c r="R29" t="n">
-        <v>7244155</v>
+        <v>7243836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,11 +3424,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3453,7 +3453,7 @@
         <v>125831881</v>
       </c>
       <c r="B30" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>125831889</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>125831880</v>
       </c>
       <c r="B32" t="n">
-        <v>91387</v>
+        <v>91388</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,10 +4429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125831894</v>
+        <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4440,21 +4440,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768196</v>
+        <v>768184</v>
       </c>
       <c r="R40" t="n">
-        <v>7244226</v>
+        <v>7244205</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125831850</v>
+        <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4537,21 +4537,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>768184</v>
+        <v>768196</v>
       </c>
       <c r="R41" t="n">
-        <v>7244205</v>
+        <v>7244226</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831896</v>
+        <v>125831853</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768175</v>
+        <v>768115</v>
       </c>
       <c r="R4" t="n">
-        <v>7244238</v>
+        <v>7244249</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831876</v>
+        <v>125831896</v>
       </c>
       <c r="B5" t="n">
-        <v>5479</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768216</v>
+        <v>768175</v>
       </c>
       <c r="R5" t="n">
-        <v>7244197</v>
+        <v>7244238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831853</v>
+        <v>125831876</v>
       </c>
       <c r="B6" t="n">
-        <v>79000</v>
+        <v>5479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768115</v>
+        <v>768216</v>
       </c>
       <c r="R6" t="n">
-        <v>7244249</v>
+        <v>7244197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831866</v>
+        <v>125831873</v>
       </c>
       <c r="B10" t="n">
-        <v>57811</v>
+        <v>92710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768107</v>
+        <v>768223</v>
       </c>
       <c r="R10" t="n">
-        <v>7244257</v>
+        <v>7244174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831885</v>
+        <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768166</v>
+        <v>768107</v>
       </c>
       <c r="R11" t="n">
-        <v>7244249</v>
+        <v>7244257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,7 +1641,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1660,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831873</v>
+        <v>125831885</v>
       </c>
       <c r="B12" t="n">
-        <v>92708</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1670,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768223</v>
+        <v>768166</v>
       </c>
       <c r="R12" t="n">
-        <v>7244174</v>
+        <v>7244249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1739,6 +1738,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831886</v>
+        <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768160</v>
+        <v>768152</v>
       </c>
       <c r="R15" t="n">
-        <v>7244178</v>
+        <v>7244247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831902</v>
+        <v>125831863</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,34 +2059,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768129</v>
+        <v>768181</v>
       </c>
       <c r="R16" t="n">
-        <v>7244186</v>
+        <v>7244196</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2127,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831852</v>
+        <v>125831886</v>
       </c>
       <c r="B17" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2169,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768152</v>
+        <v>768160</v>
       </c>
       <c r="R17" t="n">
-        <v>7244247</v>
+        <v>7244178</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831863</v>
+        <v>125831902</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,42 +2266,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768181</v>
+        <v>768129</v>
       </c>
       <c r="R18" t="n">
-        <v>7244196</v>
+        <v>7244186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2321,11 +2326,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,49 +2656,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831862</v>
+        <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768217</v>
+        <v>768218</v>
       </c>
       <c r="R22" t="n">
-        <v>7244177</v>
+        <v>7244090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,11 +2727,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2762,7 +2753,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831891</v>
+        <v>125831899</v>
       </c>
       <c r="B23" t="n">
         <v>78968</v>
@@ -2797,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768218</v>
+        <v>768171</v>
       </c>
       <c r="R23" t="n">
-        <v>7244090</v>
+        <v>7244251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,45 +2850,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831899</v>
+        <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768171</v>
+        <v>768217</v>
       </c>
       <c r="R24" t="n">
-        <v>7244251</v>
+        <v>7244177</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2930,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831881</v>
+        <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91246</v>
+        <v>91389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768188</v>
+        <v>768186</v>
       </c>
       <c r="R30" t="n">
-        <v>7244214</v>
+        <v>7244183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831889</v>
+        <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>91246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768182</v>
+        <v>768188</v>
       </c>
       <c r="R31" t="n">
-        <v>7243990</v>
+        <v>7244214</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,32 +3644,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831880</v>
+        <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>91388</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768186</v>
+        <v>768182</v>
       </c>
       <c r="R32" t="n">
-        <v>7244183</v>
+        <v>7243990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831864</v>
+        <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57811</v>
+        <v>57648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768102</v>
+        <v>768122</v>
       </c>
       <c r="R35" t="n">
-        <v>7244258</v>
+        <v>7243923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831868</v>
+        <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>57811</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768122</v>
+        <v>768102</v>
       </c>
       <c r="R36" t="n">
-        <v>7243923</v>
+        <v>7244258</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4132,7 +4132,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92708</v>
+        <v>92710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831888</v>
+        <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768148</v>
+        <v>768115</v>
       </c>
       <c r="R3" t="n">
-        <v>7243853</v>
+        <v>7244249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831853</v>
+        <v>125831876</v>
       </c>
       <c r="B4" t="n">
-        <v>79000</v>
+        <v>5479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>101920</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768115</v>
+        <v>768216</v>
       </c>
       <c r="R4" t="n">
-        <v>7244249</v>
+        <v>7244197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,7 +967,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831896</v>
+        <v>125831888</v>
       </c>
       <c r="B5" t="n">
         <v>78968</v>
@@ -1001,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768175</v>
+        <v>768148</v>
       </c>
       <c r="R5" t="n">
-        <v>7244238</v>
+        <v>7243853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831876</v>
+        <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>5479</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768216</v>
+        <v>768175</v>
       </c>
       <c r="R6" t="n">
-        <v>7244197</v>
+        <v>7244238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1143,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831880</v>
+        <v>125831881</v>
       </c>
       <c r="B30" t="n">
-        <v>91389</v>
+        <v>91246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768186</v>
+        <v>768188</v>
       </c>
       <c r="R30" t="n">
-        <v>7244183</v>
+        <v>7244214</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831881</v>
+        <v>125831889</v>
       </c>
       <c r="B31" t="n">
-        <v>91246</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768188</v>
+        <v>768182</v>
       </c>
       <c r="R31" t="n">
-        <v>7244214</v>
+        <v>7243990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,32 +3644,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831889</v>
+        <v>125831880</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>91389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768182</v>
+        <v>768186</v>
       </c>
       <c r="R32" t="n">
-        <v>7243990</v>
+        <v>7244183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831853</v>
+        <v>125831888</v>
       </c>
       <c r="B3" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768115</v>
+        <v>768148</v>
       </c>
       <c r="R3" t="n">
-        <v>7244249</v>
+        <v>7243853</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831876</v>
+        <v>125831853</v>
       </c>
       <c r="B4" t="n">
-        <v>5479</v>
+        <v>79004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101920</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768216</v>
+        <v>768115</v>
       </c>
       <c r="R4" t="n">
-        <v>7244197</v>
+        <v>7244249</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -967,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831888</v>
+        <v>125831896</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768148</v>
+        <v>768175</v>
       </c>
       <c r="R5" t="n">
-        <v>7243853</v>
+        <v>7244238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831896</v>
+        <v>125831876</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>5479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768175</v>
+        <v>768216</v>
       </c>
       <c r="R6" t="n">
-        <v>7244238</v>
+        <v>7244197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831897</v>
+        <v>125831867</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768187</v>
+        <v>768108</v>
       </c>
       <c r="R7" t="n">
-        <v>7244255</v>
+        <v>7243943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,7 +1261,7 @@
         <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831867</v>
+        <v>125831897</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1379,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768108</v>
+        <v>768187</v>
       </c>
       <c r="R9" t="n">
-        <v>7243943</v>
+        <v>7244255</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>125831873</v>
       </c>
       <c r="B10" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831866</v>
+        <v>125831885</v>
       </c>
       <c r="B11" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768107</v>
+        <v>768166</v>
       </c>
       <c r="R11" t="n">
-        <v>7244257</v>
+        <v>7244249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,6 +1641,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1659,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831885</v>
+        <v>125831866</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1694,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768166</v>
+        <v>768107</v>
       </c>
       <c r="R12" t="n">
-        <v>7244249</v>
+        <v>7244257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,7 +1739,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831871</v>
+        <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>78992</v>
+        <v>91197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768129</v>
+        <v>768096</v>
       </c>
       <c r="R13" t="n">
-        <v>7244186</v>
+        <v>7243909</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831857</v>
+        <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>91193</v>
+        <v>78996</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768096</v>
+        <v>768129</v>
       </c>
       <c r="R14" t="n">
-        <v>7243909</v>
+        <v>7244186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831852</v>
+        <v>125831863</v>
       </c>
       <c r="B15" t="n">
-        <v>79000</v>
+        <v>57811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,34 +1962,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768152</v>
+        <v>768181</v>
       </c>
       <c r="R15" t="n">
-        <v>7244247</v>
+        <v>7244196</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,6 +2030,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831863</v>
+        <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,42 +2072,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768181</v>
+        <v>768160</v>
       </c>
       <c r="R16" t="n">
-        <v>7244196</v>
+        <v>7244178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2127,11 +2132,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831886</v>
+        <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768160</v>
+        <v>768129</v>
       </c>
       <c r="R17" t="n">
-        <v>7244178</v>
+        <v>7244186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831902</v>
+        <v>125831852</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768129</v>
+        <v>768152</v>
       </c>
       <c r="R18" t="n">
-        <v>7244186</v>
+        <v>7244247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
         <v>125831900</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>125831890</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831891</v>
+        <v>125831899</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768218</v>
+        <v>768171</v>
       </c>
       <c r="R22" t="n">
-        <v>7244090</v>
+        <v>7244251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831899</v>
+        <v>125831891</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768171</v>
+        <v>768218</v>
       </c>
       <c r="R23" t="n">
-        <v>7244251</v>
+        <v>7244090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,7 +3056,7 @@
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,49 +3150,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831861</v>
+        <v>125831851</v>
       </c>
       <c r="B27" t="n">
-        <v>56843</v>
+        <v>79004</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768249</v>
+        <v>768168</v>
       </c>
       <c r="R27" t="n">
-        <v>7244155</v>
+        <v>7244250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,11 +3221,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3256,10 +3247,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831851</v>
+        <v>125831879</v>
       </c>
       <c r="B28" t="n">
-        <v>79000</v>
+        <v>91246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3258,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3282,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768168</v>
+        <v>768140</v>
       </c>
       <c r="R28" t="n">
-        <v>7244250</v>
+        <v>7243836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3353,45 +3344,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831879</v>
+        <v>125831861</v>
       </c>
       <c r="B29" t="n">
-        <v>91242</v>
+        <v>56843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768140</v>
+        <v>768249</v>
       </c>
       <c r="R29" t="n">
-        <v>7243836</v>
+        <v>7244155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,6 +3419,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831881</v>
+        <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91246</v>
+        <v>91393</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768188</v>
+        <v>768186</v>
       </c>
       <c r="R30" t="n">
-        <v>7244214</v>
+        <v>7244183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831889</v>
+        <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>91250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768182</v>
+        <v>768188</v>
       </c>
       <c r="R31" t="n">
-        <v>7243990</v>
+        <v>7244214</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,32 +3644,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831880</v>
+        <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>91389</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768186</v>
+        <v>768182</v>
       </c>
       <c r="R32" t="n">
-        <v>7244183</v>
+        <v>7243990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831898</v>
+        <v>125831868</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>57648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768185</v>
+        <v>768122</v>
       </c>
       <c r="R33" t="n">
-        <v>7244244</v>
+        <v>7243923</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831887</v>
+        <v>125831898</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768147</v>
+        <v>768185</v>
       </c>
       <c r="R34" t="n">
-        <v>7244072</v>
+        <v>7244244</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831868</v>
+        <v>125831887</v>
       </c>
       <c r="B35" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768122</v>
+        <v>768147</v>
       </c>
       <c r="R35" t="n">
-        <v>7243923</v>
+        <v>7244072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4132,7 +4132,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831857</v>
+        <v>125831871</v>
       </c>
       <c r="B13" t="n">
-        <v>91197</v>
+        <v>78996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768096</v>
+        <v>768129</v>
       </c>
       <c r="R13" t="n">
-        <v>7243909</v>
+        <v>7244186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831871</v>
+        <v>125831857</v>
       </c>
       <c r="B14" t="n">
-        <v>78996</v>
+        <v>91197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768129</v>
+        <v>768096</v>
       </c>
       <c r="R14" t="n">
-        <v>7244186</v>
+        <v>7243909</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831863</v>
+        <v>125831886</v>
       </c>
       <c r="B15" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,42 +1962,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768181</v>
+        <v>768160</v>
       </c>
       <c r="R15" t="n">
-        <v>7244196</v>
+        <v>7244178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2061,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831886</v>
+        <v>125831863</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,34 +2059,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768160</v>
+        <v>768181</v>
       </c>
       <c r="R16" t="n">
-        <v>7244178</v>
+        <v>7244196</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,6 +2127,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831902</v>
+        <v>125831852</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768129</v>
+        <v>768152</v>
       </c>
       <c r="R17" t="n">
-        <v>7244186</v>
+        <v>7244247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831852</v>
+        <v>125831902</v>
       </c>
       <c r="B18" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768152</v>
+        <v>768129</v>
       </c>
       <c r="R18" t="n">
-        <v>7244247</v>
+        <v>7244186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831895</v>
+        <v>125831851</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768193</v>
+        <v>768168</v>
       </c>
       <c r="R26" t="n">
-        <v>7244227</v>
+        <v>7244250</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831851</v>
+        <v>125831879</v>
       </c>
       <c r="B27" t="n">
-        <v>79004</v>
+        <v>91246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768168</v>
+        <v>768140</v>
       </c>
       <c r="R27" t="n">
-        <v>7244250</v>
+        <v>7243836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831879</v>
+        <v>125831895</v>
       </c>
       <c r="B28" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3258,21 +3258,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768140</v>
+        <v>768193</v>
       </c>
       <c r="R28" t="n">
-        <v>7243836</v>
+        <v>7244227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125831874</v>
+        <v>125831901</v>
       </c>
       <c r="B37" t="n">
-        <v>92714</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768188</v>
+        <v>768103</v>
       </c>
       <c r="R37" t="n">
-        <v>7244204</v>
+        <v>7244200</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4226,10 +4226,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125831901</v>
+        <v>125831874</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>92714</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768103</v>
+        <v>768188</v>
       </c>
       <c r="R38" t="n">
-        <v>7244200</v>
+        <v>7244204</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831888</v>
+        <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768148</v>
+        <v>768115</v>
       </c>
       <c r="R3" t="n">
-        <v>7243853</v>
+        <v>7244249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831853</v>
+        <v>125831896</v>
       </c>
       <c r="B4" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768115</v>
+        <v>768175</v>
       </c>
       <c r="R4" t="n">
-        <v>7244249</v>
+        <v>7244238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831896</v>
+        <v>125831888</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768175</v>
+        <v>768148</v>
       </c>
       <c r="R5" t="n">
-        <v>7244238</v>
+        <v>7243853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831867</v>
+        <v>125831883</v>
       </c>
       <c r="B7" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,34 +1172,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768108</v>
+        <v>768238</v>
       </c>
       <c r="R7" t="n">
-        <v>7243943</v>
+        <v>7244188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1234,12 +1241,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1258,7 +1271,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831883</v>
+        <v>125831897</v>
       </c>
       <c r="B8" t="n">
         <v>78972</v>
@@ -1287,23 +1300,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768238</v>
+        <v>768187</v>
       </c>
       <c r="R8" t="n">
-        <v>7244188</v>
+        <v>7244255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,18 +1344,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831897</v>
+        <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>57648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1379,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768187</v>
+        <v>768108</v>
       </c>
       <c r="R9" t="n">
-        <v>7244255</v>
+        <v>7243943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831885</v>
+        <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768166</v>
+        <v>768107</v>
       </c>
       <c r="R11" t="n">
-        <v>7244249</v>
+        <v>7244257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,7 +1641,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1660,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831866</v>
+        <v>125831885</v>
       </c>
       <c r="B12" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1670,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768107</v>
+        <v>768166</v>
       </c>
       <c r="R12" t="n">
-        <v>7244257</v>
+        <v>7244249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1739,6 +1738,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831886</v>
+        <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768160</v>
+        <v>768152</v>
       </c>
       <c r="R15" t="n">
-        <v>7244178</v>
+        <v>7244247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831863</v>
+        <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,42 +2059,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768181</v>
+        <v>768160</v>
       </c>
       <c r="R16" t="n">
-        <v>7244196</v>
+        <v>7244178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2127,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831852</v>
+        <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768152</v>
+        <v>768129</v>
       </c>
       <c r="R17" t="n">
-        <v>7244247</v>
+        <v>7244186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831902</v>
+        <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,34 +2253,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768129</v>
+        <v>768181</v>
       </c>
       <c r="R18" t="n">
-        <v>7244186</v>
+        <v>7244196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2326,6 +2321,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,32 +2656,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831899</v>
+        <v>125831878</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>58292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103042</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768171</v>
+        <v>768177</v>
       </c>
       <c r="R22" t="n">
-        <v>7244251</v>
+        <v>7244173</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,7 +2753,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831891</v>
+        <v>125831899</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768218</v>
+        <v>768171</v>
       </c>
       <c r="R23" t="n">
-        <v>7244090</v>
+        <v>7244251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,49 +2850,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831862</v>
+        <v>125831891</v>
       </c>
       <c r="B24" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768217</v>
+        <v>768218</v>
       </c>
       <c r="R24" t="n">
-        <v>7244177</v>
+        <v>7244090</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2921,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,45 +2947,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831878</v>
+        <v>125831862</v>
       </c>
       <c r="B25" t="n">
-        <v>58292</v>
+        <v>56843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103042</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768177</v>
+        <v>768217</v>
       </c>
       <c r="R25" t="n">
-        <v>7244173</v>
+        <v>7244177</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831879</v>
+        <v>125831895</v>
       </c>
       <c r="B27" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768140</v>
+        <v>768193</v>
       </c>
       <c r="R27" t="n">
-        <v>7243836</v>
+        <v>7244227</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831895</v>
+        <v>125831879</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>91246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3258,21 +3258,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768193</v>
+        <v>768140</v>
       </c>
       <c r="R28" t="n">
-        <v>7244227</v>
+        <v>7243836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831880</v>
+        <v>125831889</v>
       </c>
       <c r="B30" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768186</v>
+        <v>768182</v>
       </c>
       <c r="R30" t="n">
-        <v>7244183</v>
+        <v>7243990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831881</v>
+        <v>125831880</v>
       </c>
       <c r="B31" t="n">
-        <v>91250</v>
+        <v>91393</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768188</v>
+        <v>768186</v>
       </c>
       <c r="R31" t="n">
-        <v>7244214</v>
+        <v>7244183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831889</v>
+        <v>125831881</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,21 +3655,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768182</v>
+        <v>768188</v>
       </c>
       <c r="R32" t="n">
-        <v>7243990</v>
+        <v>7244214</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831868</v>
+        <v>125831864</v>
       </c>
       <c r="B33" t="n">
-        <v>57648</v>
+        <v>57811</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768122</v>
+        <v>768102</v>
       </c>
       <c r="R33" t="n">
-        <v>7243923</v>
+        <v>7244258</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831864</v>
+        <v>125831868</v>
       </c>
       <c r="B36" t="n">
-        <v>57811</v>
+        <v>57648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768102</v>
+        <v>768122</v>
       </c>
       <c r="R36" t="n">
-        <v>7244258</v>
+        <v>7243923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831853</v>
+        <v>125831876</v>
       </c>
       <c r="B3" t="n">
-        <v>79004</v>
+        <v>5479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>101920</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768115</v>
+        <v>768216</v>
       </c>
       <c r="R3" t="n">
-        <v>7244249</v>
+        <v>7244197</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831896</v>
+        <v>125831853</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768175</v>
+        <v>768115</v>
       </c>
       <c r="R4" t="n">
-        <v>7244238</v>
+        <v>7244249</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +967,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831888</v>
+        <v>125831896</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1001,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768148</v>
+        <v>768175</v>
       </c>
       <c r="R5" t="n">
-        <v>7243853</v>
+        <v>7244238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831876</v>
+        <v>125831888</v>
       </c>
       <c r="B6" t="n">
-        <v>5479</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768216</v>
+        <v>768148</v>
       </c>
       <c r="R6" t="n">
-        <v>7244197</v>
+        <v>7243853</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1143,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -3450,10 +3450,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831889</v>
+        <v>125831881</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768182</v>
+        <v>768188</v>
       </c>
       <c r="R30" t="n">
-        <v>7243990</v>
+        <v>7244214</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831880</v>
+        <v>125831889</v>
       </c>
       <c r="B31" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768186</v>
+        <v>768182</v>
       </c>
       <c r="R31" t="n">
-        <v>7244183</v>
+        <v>7243990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,32 +3644,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831881</v>
+        <v>125831880</v>
       </c>
       <c r="B32" t="n">
-        <v>91250</v>
+        <v>91393</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768188</v>
+        <v>768186</v>
       </c>
       <c r="R32" t="n">
-        <v>7244214</v>
+        <v>7244183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831873</v>
+        <v>125831866</v>
       </c>
       <c r="B10" t="n">
-        <v>92714</v>
+        <v>57811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768223</v>
+        <v>768107</v>
       </c>
       <c r="R10" t="n">
-        <v>7244174</v>
+        <v>7244257</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831866</v>
+        <v>125831885</v>
       </c>
       <c r="B11" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768107</v>
+        <v>768166</v>
       </c>
       <c r="R11" t="n">
-        <v>7244257</v>
+        <v>7244249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,6 +1641,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1659,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831885</v>
+        <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>92714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1694,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768166</v>
+        <v>768223</v>
       </c>
       <c r="R12" t="n">
-        <v>7244249</v>
+        <v>7244174</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,7 +1739,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2850,45 +2850,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831891</v>
+        <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768218</v>
+        <v>768217</v>
       </c>
       <c r="R24" t="n">
-        <v>7244090</v>
+        <v>7244177</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2947,49 +2956,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831862</v>
+        <v>125831891</v>
       </c>
       <c r="B25" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768217</v>
+        <v>768218</v>
       </c>
       <c r="R25" t="n">
-        <v>7244177</v>
+        <v>7244090</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831895</v>
+        <v>125831879</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>91246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768193</v>
+        <v>768140</v>
       </c>
       <c r="R27" t="n">
-        <v>7244227</v>
+        <v>7243836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831879</v>
+        <v>125831895</v>
       </c>
       <c r="B28" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3258,21 +3258,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768140</v>
+        <v>768193</v>
       </c>
       <c r="R28" t="n">
-        <v>7243836</v>
+        <v>7244227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3450,10 +3450,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831881</v>
+        <v>125831889</v>
       </c>
       <c r="B30" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768188</v>
+        <v>768182</v>
       </c>
       <c r="R30" t="n">
-        <v>7244214</v>
+        <v>7243990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831889</v>
+        <v>125831880</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768182</v>
+        <v>768186</v>
       </c>
       <c r="R31" t="n">
-        <v>7243990</v>
+        <v>7244183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,32 +3644,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831880</v>
+        <v>125831881</v>
       </c>
       <c r="B32" t="n">
-        <v>91393</v>
+        <v>91250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768186</v>
+        <v>768188</v>
       </c>
       <c r="R32" t="n">
-        <v>7244183</v>
+        <v>7244214</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831876</v>
+        <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>5479</v>
+        <v>79005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101920</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768216</v>
+        <v>768115</v>
       </c>
       <c r="R3" t="n">
-        <v>7244197</v>
+        <v>7244249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831853</v>
+        <v>125831888</v>
       </c>
       <c r="B4" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768115</v>
+        <v>768148</v>
       </c>
       <c r="R4" t="n">
-        <v>7244249</v>
+        <v>7243853</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,7 +969,7 @@
         <v>125831896</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831888</v>
+        <v>125831876</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>5479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768148</v>
+        <v>768216</v>
       </c>
       <c r="R6" t="n">
-        <v>7243853</v>
+        <v>7244197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831883</v>
+        <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,23 +1190,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768238</v>
+        <v>768187</v>
       </c>
       <c r="R7" t="n">
-        <v>7244188</v>
+        <v>7244255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,18 +1234,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1271,10 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831897</v>
+        <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,16 +1287,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768187</v>
+        <v>768238</v>
       </c>
       <c r="R8" t="n">
-        <v>7244255</v>
+        <v>7244188</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,12 +1338,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831866</v>
+        <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>57811</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768107</v>
+        <v>768166</v>
       </c>
       <c r="R10" t="n">
-        <v>7244257</v>
+        <v>7244249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,6 +1544,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1562,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831885</v>
+        <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>57812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768166</v>
+        <v>768107</v>
       </c>
       <c r="R11" t="n">
-        <v>7244249</v>
+        <v>7244257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,7 +1642,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831871</v>
+        <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>78996</v>
+        <v>91199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768129</v>
+        <v>768096</v>
       </c>
       <c r="R13" t="n">
-        <v>7244186</v>
+        <v>7243909</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831857</v>
+        <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>91197</v>
+        <v>78997</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768096</v>
+        <v>768129</v>
       </c>
       <c r="R14" t="n">
-        <v>7243909</v>
+        <v>7244186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
         <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125831900</v>
+        <v>125831890</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>768138</v>
+        <v>768204</v>
       </c>
       <c r="R19" t="n">
-        <v>7244250</v>
+        <v>7243995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125831890</v>
+        <v>125831900</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>768204</v>
+        <v>768138</v>
       </c>
       <c r="R20" t="n">
-        <v>7243995</v>
+        <v>7244250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,45 +2656,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831878</v>
+        <v>125831862</v>
       </c>
       <c r="B22" t="n">
-        <v>58292</v>
+        <v>56844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768177</v>
+        <v>768217</v>
       </c>
       <c r="R22" t="n">
-        <v>7244173</v>
+        <v>7244177</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,6 +2731,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2753,32 +2762,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831899</v>
+        <v>125831878</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>58293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103042</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2788,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768171</v>
+        <v>768177</v>
       </c>
       <c r="R23" t="n">
-        <v>7244251</v>
+        <v>7244173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,49 +2859,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831862</v>
+        <v>125831891</v>
       </c>
       <c r="B24" t="n">
-        <v>56843</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768217</v>
+        <v>768218</v>
       </c>
       <c r="R24" t="n">
-        <v>7244177</v>
+        <v>7244090</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2930,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831891</v>
+        <v>125831899</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768218</v>
+        <v>768171</v>
       </c>
       <c r="R25" t="n">
-        <v>7244090</v>
+        <v>7244251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831851</v>
+        <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768168</v>
+        <v>768193</v>
       </c>
       <c r="R26" t="n">
-        <v>7244250</v>
+        <v>7244227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,45 +3150,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831879</v>
+        <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>91246</v>
+        <v>56844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768140</v>
+        <v>768249</v>
       </c>
       <c r="R27" t="n">
-        <v>7243836</v>
+        <v>7244155</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,6 +3225,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3247,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831895</v>
+        <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3258,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3282,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768193</v>
+        <v>768168</v>
       </c>
       <c r="R28" t="n">
-        <v>7244227</v>
+        <v>7244250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,49 +3353,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831861</v>
+        <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>56843</v>
+        <v>91248</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768249</v>
+        <v>768140</v>
       </c>
       <c r="R29" t="n">
-        <v>7244155</v>
+        <v>7243836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,11 +3424,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831889</v>
+        <v>125831881</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768182</v>
+        <v>768188</v>
       </c>
       <c r="R30" t="n">
-        <v>7243990</v>
+        <v>7244214</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
         <v>125831880</v>
       </c>
       <c r="B31" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831881</v>
+        <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>91250</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,21 +3655,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768188</v>
+        <v>768182</v>
       </c>
       <c r="R32" t="n">
-        <v>7244214</v>
+        <v>7243990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831864</v>
+        <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>57811</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768102</v>
+        <v>768185</v>
       </c>
       <c r="R33" t="n">
-        <v>7244258</v>
+        <v>7244244</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831898</v>
+        <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768185</v>
+        <v>768147</v>
       </c>
       <c r="R34" t="n">
-        <v>7244244</v>
+        <v>7244072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831887</v>
+        <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>57649</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768147</v>
+        <v>768122</v>
       </c>
       <c r="R35" t="n">
-        <v>7244072</v>
+        <v>7243923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831868</v>
+        <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>57812</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768122</v>
+        <v>768102</v>
       </c>
       <c r="R36" t="n">
-        <v>7243923</v>
+        <v>7244258</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125831901</v>
+        <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>92716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768103</v>
+        <v>768188</v>
       </c>
       <c r="R37" t="n">
-        <v>7244200</v>
+        <v>7244204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4226,10 +4226,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125831874</v>
+        <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>92714</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768188</v>
+        <v>768103</v>
       </c>
       <c r="R38" t="n">
-        <v>7244204</v>
+        <v>7244200</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4326,7 +4326,7 @@
         <v>125831860</v>
       </c>
       <c r="B39" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831852</v>
+        <v>125831863</v>
       </c>
       <c r="B15" t="n">
-        <v>79005</v>
+        <v>57812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,34 +1962,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768152</v>
+        <v>768181</v>
       </c>
       <c r="R15" t="n">
-        <v>7244247</v>
+        <v>7244196</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,6 +2030,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831886</v>
+        <v>125831852</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768160</v>
+        <v>768152</v>
       </c>
       <c r="R16" t="n">
-        <v>7244178</v>
+        <v>7244247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2158,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831902</v>
+        <v>125831886</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2180,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768129</v>
+        <v>768160</v>
       </c>
       <c r="R17" t="n">
-        <v>7244186</v>
+        <v>7244178</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831863</v>
+        <v>125831902</v>
       </c>
       <c r="B18" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,42 +2266,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768181</v>
+        <v>768129</v>
       </c>
       <c r="R18" t="n">
-        <v>7244196</v>
+        <v>7244186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2321,11 +2326,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831888</v>
+        <v>125831896</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768148</v>
+        <v>768175</v>
       </c>
       <c r="R4" t="n">
-        <v>7243853</v>
+        <v>7244238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831896</v>
+        <v>125831888</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768175</v>
+        <v>768148</v>
       </c>
       <c r="R5" t="n">
-        <v>7244238</v>
+        <v>7243853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831897</v>
+        <v>125831883</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1190,16 +1190,23 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768187</v>
+        <v>768238</v>
       </c>
       <c r="R7" t="n">
-        <v>7244255</v>
+        <v>7244188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1234,12 +1241,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1258,7 +1271,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831883</v>
+        <v>125831897</v>
       </c>
       <c r="B8" t="n">
         <v>78973</v>
@@ -1287,23 +1300,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768238</v>
+        <v>768187</v>
       </c>
       <c r="R8" t="n">
-        <v>7244188</v>
+        <v>7244255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,18 +1344,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831885</v>
+        <v>125831873</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>92718</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768166</v>
+        <v>768223</v>
       </c>
       <c r="R10" t="n">
-        <v>7244249</v>
+        <v>7244174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1544,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1563,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831866</v>
+        <v>125831885</v>
       </c>
       <c r="B11" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768107</v>
+        <v>768166</v>
       </c>
       <c r="R11" t="n">
-        <v>7244257</v>
+        <v>7244249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1642,6 +1641,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831873</v>
+        <v>125831866</v>
       </c>
       <c r="B12" t="n">
-        <v>92716</v>
+        <v>57812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768223</v>
+        <v>768107</v>
       </c>
       <c r="R12" t="n">
-        <v>7244174</v>
+        <v>7244257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831863</v>
+        <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>57812</v>
+        <v>79005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,42 +1962,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768181</v>
+        <v>768152</v>
       </c>
       <c r="R15" t="n">
-        <v>7244196</v>
+        <v>7244247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2061,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831852</v>
+        <v>125831902</v>
       </c>
       <c r="B16" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768152</v>
+        <v>768129</v>
       </c>
       <c r="R16" t="n">
-        <v>7244247</v>
+        <v>7244186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831902</v>
+        <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,34 +2253,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768129</v>
+        <v>768181</v>
       </c>
       <c r="R18" t="n">
-        <v>7244186</v>
+        <v>7244196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2326,6 +2321,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2352,7 +2352,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125831890</v>
+        <v>125831900</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>768204</v>
+        <v>768138</v>
       </c>
       <c r="R19" t="n">
-        <v>7243995</v>
+        <v>7244250</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125831900</v>
+        <v>125831890</v>
       </c>
       <c r="B20" t="n">
         <v>78973</v>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>768138</v>
+        <v>768204</v>
       </c>
       <c r="R20" t="n">
-        <v>7244250</v>
+        <v>7243995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,49 +2656,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831862</v>
+        <v>125831899</v>
       </c>
       <c r="B22" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768217</v>
+        <v>768171</v>
       </c>
       <c r="R22" t="n">
-        <v>7244177</v>
+        <v>7244251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,11 +2727,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2762,32 +2753,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831878</v>
+        <v>125831891</v>
       </c>
       <c r="B23" t="n">
-        <v>58293</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2797,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768177</v>
+        <v>768218</v>
       </c>
       <c r="R23" t="n">
-        <v>7244173</v>
+        <v>7244090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,32 +2850,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831891</v>
+        <v>125831878</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>58293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103042</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768218</v>
+        <v>768177</v>
       </c>
       <c r="R24" t="n">
-        <v>7244090</v>
+        <v>7244173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2956,45 +2947,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831899</v>
+        <v>125831862</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768171</v>
+        <v>768217</v>
       </c>
       <c r="R25" t="n">
-        <v>7244251</v>
+        <v>7244177</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831895</v>
+        <v>125831851</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768193</v>
+        <v>768168</v>
       </c>
       <c r="R26" t="n">
-        <v>7244227</v>
+        <v>7244250</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,49 +3150,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831861</v>
+        <v>125831879</v>
       </c>
       <c r="B27" t="n">
-        <v>56844</v>
+        <v>91250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768249</v>
+        <v>768140</v>
       </c>
       <c r="R27" t="n">
-        <v>7244155</v>
+        <v>7243836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,11 +3221,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3256,10 +3247,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831851</v>
+        <v>125831895</v>
       </c>
       <c r="B28" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3258,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3282,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768168</v>
+        <v>768193</v>
       </c>
       <c r="R28" t="n">
-        <v>7244250</v>
+        <v>7244227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3353,45 +3344,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831879</v>
+        <v>125831861</v>
       </c>
       <c r="B29" t="n">
-        <v>91248</v>
+        <v>56844</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768140</v>
+        <v>768249</v>
       </c>
       <c r="R29" t="n">
-        <v>7243836</v>
+        <v>7244155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,6 +3419,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831881</v>
+        <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91252</v>
+        <v>91397</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768188</v>
+        <v>768186</v>
       </c>
       <c r="R30" t="n">
-        <v>7244214</v>
+        <v>7244183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831880</v>
+        <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91395</v>
+        <v>91254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768186</v>
+        <v>768188</v>
       </c>
       <c r="R31" t="n">
-        <v>7244183</v>
+        <v>7244214</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831898</v>
+        <v>125831864</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768185</v>
+        <v>768102</v>
       </c>
       <c r="R33" t="n">
-        <v>7244244</v>
+        <v>7244258</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831887</v>
+        <v>125831898</v>
       </c>
       <c r="B34" t="n">
         <v>78973</v>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768147</v>
+        <v>768185</v>
       </c>
       <c r="R34" t="n">
-        <v>7244072</v>
+        <v>7244244</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831868</v>
+        <v>125831887</v>
       </c>
       <c r="B35" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768122</v>
+        <v>768147</v>
       </c>
       <c r="R35" t="n">
-        <v>7243923</v>
+        <v>7244072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831864</v>
+        <v>125831868</v>
       </c>
       <c r="B36" t="n">
-        <v>57812</v>
+        <v>57649</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768102</v>
+        <v>768122</v>
       </c>
       <c r="R36" t="n">
-        <v>7244258</v>
+        <v>7243923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4132,7 +4132,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831885</v>
+        <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768166</v>
+        <v>768107</v>
       </c>
       <c r="R11" t="n">
-        <v>7244249</v>
+        <v>7244257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,7 +1641,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1660,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831866</v>
+        <v>125831885</v>
       </c>
       <c r="B12" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1670,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768107</v>
+        <v>768166</v>
       </c>
       <c r="R12" t="n">
-        <v>7244257</v>
+        <v>7244249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1739,6 +1738,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2656,45 +2656,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831899</v>
+        <v>125831862</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768171</v>
+        <v>768217</v>
       </c>
       <c r="R22" t="n">
-        <v>7244251</v>
+        <v>7244177</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,6 +2731,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2753,7 +2762,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831891</v>
+        <v>125831899</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2788,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768218</v>
+        <v>768171</v>
       </c>
       <c r="R23" t="n">
-        <v>7244090</v>
+        <v>7244251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,32 +2859,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831878</v>
+        <v>125831891</v>
       </c>
       <c r="B24" t="n">
-        <v>58293</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103042</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768177</v>
+        <v>768218</v>
       </c>
       <c r="R24" t="n">
-        <v>7244173</v>
+        <v>7244090</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,49 +2956,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831862</v>
+        <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>56844</v>
+        <v>58293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>103042</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768217</v>
+        <v>768177</v>
       </c>
       <c r="R25" t="n">
-        <v>7244177</v>
+        <v>7244173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125831874</v>
+        <v>125831901</v>
       </c>
       <c r="B37" t="n">
-        <v>92718</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768188</v>
+        <v>768103</v>
       </c>
       <c r="R37" t="n">
-        <v>7244204</v>
+        <v>7244200</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4226,10 +4226,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125831901</v>
+        <v>125831874</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>92718</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768103</v>
+        <v>768188</v>
       </c>
       <c r="R38" t="n">
-        <v>7244200</v>
+        <v>7244204</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831853</v>
+        <v>125831888</v>
       </c>
       <c r="B3" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768115</v>
+        <v>768148</v>
       </c>
       <c r="R3" t="n">
-        <v>7244249</v>
+        <v>7243853</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831888</v>
+        <v>125831853</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768148</v>
+        <v>768115</v>
       </c>
       <c r="R5" t="n">
-        <v>7243853</v>
+        <v>7244249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831883</v>
+        <v>125831897</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1190,23 +1190,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768238</v>
+        <v>768187</v>
       </c>
       <c r="R7" t="n">
-        <v>7244188</v>
+        <v>7244255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,18 +1234,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1271,7 +1258,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831897</v>
+        <v>125831883</v>
       </c>
       <c r="B8" t="n">
         <v>78973</v>
@@ -1300,16 +1287,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768187</v>
+        <v>768238</v>
       </c>
       <c r="R8" t="n">
-        <v>7244255</v>
+        <v>7244188</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,12 +1338,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831873</v>
+        <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>92718</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768223</v>
+        <v>768166</v>
       </c>
       <c r="R10" t="n">
-        <v>7244174</v>
+        <v>7244249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,6 +1544,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1562,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831866</v>
+        <v>125831873</v>
       </c>
       <c r="B11" t="n">
-        <v>57812</v>
+        <v>92720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768107</v>
+        <v>768223</v>
       </c>
       <c r="R11" t="n">
-        <v>7244257</v>
+        <v>7244174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831885</v>
+        <v>125831866</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1694,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768166</v>
+        <v>768107</v>
       </c>
       <c r="R12" t="n">
-        <v>7244249</v>
+        <v>7244257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,7 +1739,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831857</v>
+        <v>125831871</v>
       </c>
       <c r="B13" t="n">
-        <v>91201</v>
+        <v>78997</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768096</v>
+        <v>768129</v>
       </c>
       <c r="R13" t="n">
-        <v>7243909</v>
+        <v>7244186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831871</v>
+        <v>125831857</v>
       </c>
       <c r="B14" t="n">
-        <v>78997</v>
+        <v>91203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768129</v>
+        <v>768096</v>
       </c>
       <c r="R14" t="n">
-        <v>7244186</v>
+        <v>7243909</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831852</v>
+        <v>125831886</v>
       </c>
       <c r="B15" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768152</v>
+        <v>768160</v>
       </c>
       <c r="R15" t="n">
-        <v>7244247</v>
+        <v>7244178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831886</v>
+        <v>125831852</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768160</v>
+        <v>768152</v>
       </c>
       <c r="R17" t="n">
-        <v>7244178</v>
+        <v>7244247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2656,49 +2656,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831862</v>
+        <v>125831878</v>
       </c>
       <c r="B22" t="n">
-        <v>56844</v>
+        <v>58293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>103042</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768217</v>
+        <v>768177</v>
       </c>
       <c r="R22" t="n">
-        <v>7244177</v>
+        <v>7244173</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,11 +2727,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2762,7 +2753,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831899</v>
+        <v>125831891</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2797,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768171</v>
+        <v>768218</v>
       </c>
       <c r="R23" t="n">
-        <v>7244251</v>
+        <v>7244090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,7 +2850,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831891</v>
+        <v>125831899</v>
       </c>
       <c r="B24" t="n">
         <v>78973</v>
@@ -2894,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768218</v>
+        <v>768171</v>
       </c>
       <c r="R24" t="n">
-        <v>7244090</v>
+        <v>7244251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2956,45 +2947,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831878</v>
+        <v>125831862</v>
       </c>
       <c r="B25" t="n">
-        <v>58293</v>
+        <v>56844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103042</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768177</v>
+        <v>768217</v>
       </c>
       <c r="R25" t="n">
-        <v>7244173</v>
+        <v>7244177</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831851</v>
+        <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768168</v>
+        <v>768193</v>
       </c>
       <c r="R26" t="n">
-        <v>7244250</v>
+        <v>7244227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,45 +3150,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831879</v>
+        <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>91250</v>
+        <v>56844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768140</v>
+        <v>768249</v>
       </c>
       <c r="R27" t="n">
-        <v>7243836</v>
+        <v>7244155</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,6 +3225,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3247,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831895</v>
+        <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3258,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3282,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768193</v>
+        <v>768168</v>
       </c>
       <c r="R28" t="n">
-        <v>7244227</v>
+        <v>7244250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,49 +3353,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831861</v>
+        <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>56844</v>
+        <v>91252</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768249</v>
+        <v>768140</v>
       </c>
       <c r="R29" t="n">
-        <v>7244155</v>
+        <v>7243836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,11 +3424,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831880</v>
+        <v>125831889</v>
       </c>
       <c r="B30" t="n">
-        <v>91397</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768186</v>
+        <v>768182</v>
       </c>
       <c r="R30" t="n">
-        <v>7244183</v>
+        <v>7243990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831881</v>
+        <v>125831880</v>
       </c>
       <c r="B31" t="n">
-        <v>91254</v>
+        <v>91399</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768188</v>
+        <v>768186</v>
       </c>
       <c r="R31" t="n">
-        <v>7244214</v>
+        <v>7244183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831889</v>
+        <v>125831881</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,21 +3655,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768182</v>
+        <v>768188</v>
       </c>
       <c r="R32" t="n">
-        <v>7243990</v>
+        <v>7244214</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831864</v>
+        <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768102</v>
+        <v>768185</v>
       </c>
       <c r="R33" t="n">
-        <v>7244258</v>
+        <v>7244244</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831898</v>
+        <v>125831887</v>
       </c>
       <c r="B34" t="n">
         <v>78973</v>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768185</v>
+        <v>768147</v>
       </c>
       <c r="R34" t="n">
-        <v>7244244</v>
+        <v>7244072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831887</v>
+        <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768147</v>
+        <v>768122</v>
       </c>
       <c r="R35" t="n">
-        <v>7244072</v>
+        <v>7243923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831868</v>
+        <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57649</v>
+        <v>57812</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768122</v>
+        <v>768102</v>
       </c>
       <c r="R36" t="n">
-        <v>7243923</v>
+        <v>7244258</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,7 +4229,7 @@
         <v>125831874</v>
       </c>
       <c r="B38" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125831855</v>
+        <v>125831892</v>
       </c>
       <c r="B42" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4634,21 +4634,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>768211</v>
+        <v>768218</v>
       </c>
       <c r="R42" t="n">
-        <v>7244074</v>
+        <v>7244142</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125831854</v>
+        <v>125831893</v>
       </c>
       <c r="B43" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>768124</v>
+        <v>768199</v>
       </c>
       <c r="R43" t="n">
-        <v>7244210</v>
+        <v>7244222</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125831892</v>
+        <v>125831855</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>768218</v>
+        <v>768211</v>
       </c>
       <c r="R44" t="n">
-        <v>7244142</v>
+        <v>7244074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125831893</v>
+        <v>125831854</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>768199</v>
+        <v>768124</v>
       </c>
       <c r="R45" t="n">
-        <v>7244222</v>
+        <v>7244210</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831896</v>
+        <v>125831853</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768175</v>
+        <v>768115</v>
       </c>
       <c r="R4" t="n">
-        <v>7244238</v>
+        <v>7244249</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831853</v>
+        <v>125831876</v>
       </c>
       <c r="B5" t="n">
-        <v>79005</v>
+        <v>5479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>101920</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768115</v>
+        <v>768216</v>
       </c>
       <c r="R5" t="n">
-        <v>7244249</v>
+        <v>7244197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1063,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831876</v>
+        <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>5479</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768216</v>
+        <v>768175</v>
       </c>
       <c r="R6" t="n">
-        <v>7244197</v>
+        <v>7244238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1143,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125831901</v>
+        <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>92720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768103</v>
+        <v>768188</v>
       </c>
       <c r="R37" t="n">
-        <v>7244200</v>
+        <v>7244204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4226,10 +4226,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125831874</v>
+        <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>92720</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768188</v>
+        <v>768103</v>
       </c>
       <c r="R38" t="n">
-        <v>7244204</v>
+        <v>7244200</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831888</v>
+        <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768148</v>
+        <v>768115</v>
       </c>
       <c r="R3" t="n">
-        <v>7243853</v>
+        <v>7244249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831853</v>
+        <v>125831896</v>
       </c>
       <c r="B4" t="n">
-        <v>79005</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768115</v>
+        <v>768175</v>
       </c>
       <c r="R4" t="n">
-        <v>7244249</v>
+        <v>7244238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831876</v>
+        <v>125831888</v>
       </c>
       <c r="B5" t="n">
-        <v>5479</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768216</v>
+        <v>768148</v>
       </c>
       <c r="R5" t="n">
-        <v>7244197</v>
+        <v>7243853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831896</v>
+        <v>125831876</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>5479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768175</v>
+        <v>768216</v>
       </c>
       <c r="R6" t="n">
-        <v>7244238</v>
+        <v>7244197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831897</v>
+        <v>125831883</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,16 +1190,23 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768187</v>
+        <v>768238</v>
       </c>
       <c r="R7" t="n">
-        <v>7244255</v>
+        <v>7244188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1234,12 +1241,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831883</v>
+        <v>125831897</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,23 +1300,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768238</v>
+        <v>768187</v>
       </c>
       <c r="R8" t="n">
-        <v>7244188</v>
+        <v>7244255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,18 +1344,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831885</v>
+        <v>125831873</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>92724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768166</v>
+        <v>768223</v>
       </c>
       <c r="R10" t="n">
-        <v>7244249</v>
+        <v>7244174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1544,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1563,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831873</v>
+        <v>125831885</v>
       </c>
       <c r="B11" t="n">
-        <v>92720</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768223</v>
+        <v>768166</v>
       </c>
       <c r="R11" t="n">
-        <v>7244174</v>
+        <v>7244249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1642,6 +1641,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>125831866</v>
       </c>
       <c r="B12" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831871</v>
+        <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>78997</v>
+        <v>91207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768129</v>
+        <v>768096</v>
       </c>
       <c r="R13" t="n">
-        <v>7244186</v>
+        <v>7243909</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831857</v>
+        <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>91203</v>
+        <v>79001</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768096</v>
+        <v>768129</v>
       </c>
       <c r="R14" t="n">
-        <v>7243909</v>
+        <v>7244186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831886</v>
+        <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768160</v>
+        <v>768152</v>
       </c>
       <c r="R15" t="n">
-        <v>7244178</v>
+        <v>7244247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831902</v>
+        <v>125831863</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>57816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,34 +2059,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768129</v>
+        <v>768181</v>
       </c>
       <c r="R16" t="n">
-        <v>7244186</v>
+        <v>7244196</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2127,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831852</v>
+        <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>79005</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2169,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768152</v>
+        <v>768129</v>
       </c>
       <c r="R17" t="n">
-        <v>7244247</v>
+        <v>7244186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831863</v>
+        <v>125831886</v>
       </c>
       <c r="B18" t="n">
-        <v>57812</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,42 +2266,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768181</v>
+        <v>768160</v>
       </c>
       <c r="R18" t="n">
-        <v>7244196</v>
+        <v>7244178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2321,11 +2326,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2355,7 +2355,7 @@
         <v>125831900</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>125831890</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,32 +2656,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831878</v>
+        <v>125831899</v>
       </c>
       <c r="B22" t="n">
-        <v>58293</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768177</v>
+        <v>768171</v>
       </c>
       <c r="R22" t="n">
-        <v>7244173</v>
+        <v>7244251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
         <v>125831891</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,45 +2850,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831899</v>
+        <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>56848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768171</v>
+        <v>768217</v>
       </c>
       <c r="R24" t="n">
-        <v>7244251</v>
+        <v>7244177</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2947,49 +2956,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831862</v>
+        <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>56844</v>
+        <v>58297</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>103042</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768217</v>
+        <v>768177</v>
       </c>
       <c r="R25" t="n">
-        <v>7244177</v>
+        <v>7244173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831895</v>
+        <v>125831879</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768193</v>
+        <v>768140</v>
       </c>
       <c r="R26" t="n">
-        <v>7244227</v>
+        <v>7243836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,7 +3153,7 @@
         <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831879</v>
+        <v>125831895</v>
       </c>
       <c r="B29" t="n">
-        <v>91252</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,21 +3364,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768140</v>
+        <v>768193</v>
       </c>
       <c r="R29" t="n">
-        <v>7243836</v>
+        <v>7244227</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831889</v>
+        <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>91403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768182</v>
+        <v>768186</v>
       </c>
       <c r="R30" t="n">
-        <v>7243990</v>
+        <v>7244183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831880</v>
+        <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91399</v>
+        <v>91260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768186</v>
+        <v>768188</v>
       </c>
       <c r="R31" t="n">
-        <v>7244183</v>
+        <v>7244214</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831881</v>
+        <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,21 +3655,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768188</v>
+        <v>768182</v>
       </c>
       <c r="R32" t="n">
-        <v>7244214</v>
+        <v>7243990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3744,7 +3744,7 @@
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125831874</v>
+        <v>125831901</v>
       </c>
       <c r="B37" t="n">
-        <v>92720</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768188</v>
+        <v>768103</v>
       </c>
       <c r="R37" t="n">
-        <v>7244204</v>
+        <v>7244200</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4226,10 +4226,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125831901</v>
+        <v>125831874</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>92724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768103</v>
+        <v>768188</v>
       </c>
       <c r="R38" t="n">
-        <v>7244200</v>
+        <v>7244204</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4326,7 +4326,7 @@
         <v>125831860</v>
       </c>
       <c r="B39" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>125831892</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125831893</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>125831855</v>
       </c>
       <c r="B44" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>125831854</v>
       </c>
       <c r="B45" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831853</v>
+        <v>125831896</v>
       </c>
       <c r="B3" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768115</v>
+        <v>768175</v>
       </c>
       <c r="R3" t="n">
-        <v>7244249</v>
+        <v>7244238</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831896</v>
+        <v>125831888</v>
       </c>
       <c r="B4" t="n">
         <v>78977</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768175</v>
+        <v>768148</v>
       </c>
       <c r="R4" t="n">
-        <v>7244238</v>
+        <v>7243853</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831888</v>
+        <v>125831876</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>5479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768148</v>
+        <v>768216</v>
       </c>
       <c r="R5" t="n">
-        <v>7243853</v>
+        <v>7244197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1063,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831876</v>
+        <v>125831853</v>
       </c>
       <c r="B6" t="n">
-        <v>5479</v>
+        <v>79009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768216</v>
+        <v>768115</v>
       </c>
       <c r="R6" t="n">
-        <v>7244197</v>
+        <v>7244249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1143,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831873</v>
+        <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768223</v>
+        <v>768166</v>
       </c>
       <c r="R10" t="n">
-        <v>7244174</v>
+        <v>7244249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,6 +1544,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1562,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831885</v>
+        <v>125831873</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768166</v>
+        <v>768223</v>
       </c>
       <c r="R11" t="n">
-        <v>7244249</v>
+        <v>7244174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,7 +1642,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831896</v>
+        <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768175</v>
+        <v>768115</v>
       </c>
       <c r="R3" t="n">
-        <v>7244238</v>
+        <v>7244249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831876</v>
+        <v>125831896</v>
       </c>
       <c r="B5" t="n">
-        <v>5479</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768216</v>
+        <v>768175</v>
       </c>
       <c r="R5" t="n">
-        <v>7244197</v>
+        <v>7244238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831853</v>
+        <v>125831876</v>
       </c>
       <c r="B6" t="n">
-        <v>79009</v>
+        <v>5479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768115</v>
+        <v>768216</v>
       </c>
       <c r="R6" t="n">
-        <v>7244249</v>
+        <v>7244197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831883</v>
+        <v>125831897</v>
       </c>
       <c r="B7" t="n">
         <v>78977</v>
@@ -1190,23 +1190,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768238</v>
+        <v>768187</v>
       </c>
       <c r="R7" t="n">
-        <v>7244188</v>
+        <v>7244255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,18 +1234,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1271,7 +1258,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831897</v>
+        <v>125831883</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1300,16 +1287,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768187</v>
+        <v>768238</v>
       </c>
       <c r="R8" t="n">
-        <v>7244255</v>
+        <v>7244188</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,12 +1338,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831857</v>
+        <v>125831871</v>
       </c>
       <c r="B13" t="n">
-        <v>91207</v>
+        <v>79001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768096</v>
+        <v>768129</v>
       </c>
       <c r="R13" t="n">
-        <v>7243909</v>
+        <v>7244186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831871</v>
+        <v>125831857</v>
       </c>
       <c r="B14" t="n">
-        <v>79001</v>
+        <v>91207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768129</v>
+        <v>768096</v>
       </c>
       <c r="R14" t="n">
-        <v>7244186</v>
+        <v>7243909</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831852</v>
+        <v>125831886</v>
       </c>
       <c r="B15" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768152</v>
+        <v>768160</v>
       </c>
       <c r="R15" t="n">
-        <v>7244247</v>
+        <v>7244178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831863</v>
+        <v>125831902</v>
       </c>
       <c r="B16" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,42 +2059,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768181</v>
+        <v>768129</v>
       </c>
       <c r="R16" t="n">
-        <v>7244196</v>
+        <v>7244186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2127,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831902</v>
+        <v>125831852</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768129</v>
+        <v>768152</v>
       </c>
       <c r="R17" t="n">
-        <v>7244186</v>
+        <v>7244247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831886</v>
+        <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,34 +2253,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768160</v>
+        <v>768181</v>
       </c>
       <c r="R18" t="n">
-        <v>7244178</v>
+        <v>7244196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2326,6 +2321,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,7 +2656,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125831899</v>
+        <v>125831891</v>
       </c>
       <c r="B22" t="n">
         <v>78977</v>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768171</v>
+        <v>768218</v>
       </c>
       <c r="R22" t="n">
-        <v>7244251</v>
+        <v>7244090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,7 +2753,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831891</v>
+        <v>125831899</v>
       </c>
       <c r="B23" t="n">
         <v>78977</v>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768218</v>
+        <v>768171</v>
       </c>
       <c r="R23" t="n">
-        <v>7244090</v>
+        <v>7244251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831879</v>
+        <v>125831851</v>
       </c>
       <c r="B26" t="n">
-        <v>91256</v>
+        <v>79009</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768140</v>
+        <v>768168</v>
       </c>
       <c r="R26" t="n">
-        <v>7243836</v>
+        <v>7244250</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,49 +3150,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831861</v>
+        <v>125831879</v>
       </c>
       <c r="B27" t="n">
-        <v>56848</v>
+        <v>91256</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768249</v>
+        <v>768140</v>
       </c>
       <c r="R27" t="n">
-        <v>7244155</v>
+        <v>7243836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,11 +3221,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3256,10 +3247,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831851</v>
+        <v>125831895</v>
       </c>
       <c r="B28" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3258,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3282,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768168</v>
+        <v>768193</v>
       </c>
       <c r="R28" t="n">
-        <v>7244250</v>
+        <v>7244227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3353,45 +3344,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831895</v>
+        <v>125831861</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768193</v>
+        <v>768249</v>
       </c>
       <c r="R29" t="n">
-        <v>7244227</v>
+        <v>7244155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,6 +3419,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831881</v>
+        <v>125831889</v>
       </c>
       <c r="B31" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768188</v>
+        <v>768182</v>
       </c>
       <c r="R31" t="n">
-        <v>7244214</v>
+        <v>7243990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831889</v>
+        <v>125831881</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,21 +3655,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768182</v>
+        <v>768188</v>
       </c>
       <c r="R32" t="n">
-        <v>7243990</v>
+        <v>7244214</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831898</v>
+        <v>125831864</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768185</v>
+        <v>768102</v>
       </c>
       <c r="R33" t="n">
-        <v>7244244</v>
+        <v>7244258</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831887</v>
+        <v>125831898</v>
       </c>
       <c r="B34" t="n">
         <v>78977</v>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768147</v>
+        <v>768185</v>
       </c>
       <c r="R34" t="n">
-        <v>7244072</v>
+        <v>7244244</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831868</v>
+        <v>125831887</v>
       </c>
       <c r="B35" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768122</v>
+        <v>768147</v>
       </c>
       <c r="R35" t="n">
-        <v>7243923</v>
+        <v>7244072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831864</v>
+        <v>125831868</v>
       </c>
       <c r="B36" t="n">
-        <v>57816</v>
+        <v>57653</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768102</v>
+        <v>768122</v>
       </c>
       <c r="R36" t="n">
-        <v>7244258</v>
+        <v>7243923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4429,10 +4429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125831850</v>
+        <v>125831894</v>
       </c>
       <c r="B40" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4440,21 +4440,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768184</v>
+        <v>768196</v>
       </c>
       <c r="R40" t="n">
-        <v>7244205</v>
+        <v>7244226</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125831894</v>
+        <v>125831850</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4537,21 +4537,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>768196</v>
+        <v>768184</v>
       </c>
       <c r="R41" t="n">
-        <v>7244226</v>
+        <v>7244205</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831853</v>
+        <v>125831888</v>
       </c>
       <c r="B3" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768115</v>
+        <v>768148</v>
       </c>
       <c r="R3" t="n">
-        <v>7244249</v>
+        <v>7243853</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831888</v>
+        <v>125831896</v>
       </c>
       <c r="B4" t="n">
         <v>78977</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768148</v>
+        <v>768175</v>
       </c>
       <c r="R4" t="n">
-        <v>7243853</v>
+        <v>7244238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831896</v>
+        <v>125831876</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>5479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768175</v>
+        <v>768216</v>
       </c>
       <c r="R5" t="n">
-        <v>7244238</v>
+        <v>7244197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1063,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831876</v>
+        <v>125831853</v>
       </c>
       <c r="B6" t="n">
-        <v>5479</v>
+        <v>79009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768216</v>
+        <v>768115</v>
       </c>
       <c r="R6" t="n">
-        <v>7244197</v>
+        <v>7244249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1143,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -3053,45 +3053,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831851</v>
+        <v>125831861</v>
       </c>
       <c r="B26" t="n">
-        <v>79009</v>
+        <v>56848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768168</v>
+        <v>768249</v>
       </c>
       <c r="R26" t="n">
-        <v>7244250</v>
+        <v>7244155</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3124,6 +3128,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3150,10 +3159,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831879</v>
+        <v>125831895</v>
       </c>
       <c r="B27" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3170,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3194,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768140</v>
+        <v>768193</v>
       </c>
       <c r="R27" t="n">
-        <v>7243836</v>
+        <v>7244227</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3247,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831895</v>
+        <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3258,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3282,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768193</v>
+        <v>768168</v>
       </c>
       <c r="R28" t="n">
-        <v>7244227</v>
+        <v>7244250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,49 +3353,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831861</v>
+        <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>56848</v>
+        <v>91256</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768249</v>
+        <v>768140</v>
       </c>
       <c r="R29" t="n">
-        <v>7244155</v>
+        <v>7243836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,11 +3424,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,10 +3741,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831864</v>
+        <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768102</v>
+        <v>768185</v>
       </c>
       <c r="R33" t="n">
-        <v>7244258</v>
+        <v>7244244</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831898</v>
+        <v>125831887</v>
       </c>
       <c r="B34" t="n">
         <v>78977</v>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768185</v>
+        <v>768147</v>
       </c>
       <c r="R34" t="n">
-        <v>7244244</v>
+        <v>7244072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831887</v>
+        <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768147</v>
+        <v>768122</v>
       </c>
       <c r="R35" t="n">
-        <v>7244072</v>
+        <v>7243923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831868</v>
+        <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57653</v>
+        <v>57816</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768122</v>
+        <v>768102</v>
       </c>
       <c r="R36" t="n">
-        <v>7243923</v>
+        <v>7244258</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831888</v>
+        <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768148</v>
+        <v>768115</v>
       </c>
       <c r="R3" t="n">
-        <v>7243853</v>
+        <v>7244249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831896</v>
+        <v>125831888</v>
       </c>
       <c r="B4" t="n">
         <v>78977</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768175</v>
+        <v>768148</v>
       </c>
       <c r="R4" t="n">
-        <v>7244238</v>
+        <v>7243853</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831876</v>
+        <v>125831896</v>
       </c>
       <c r="B5" t="n">
-        <v>5479</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768216</v>
+        <v>768175</v>
       </c>
       <c r="R5" t="n">
-        <v>7244197</v>
+        <v>7244238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831853</v>
+        <v>125831876</v>
       </c>
       <c r="B6" t="n">
-        <v>79009</v>
+        <v>5479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768115</v>
+        <v>768216</v>
       </c>
       <c r="R6" t="n">
-        <v>7244249</v>
+        <v>7244197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831885</v>
+        <v>125831873</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768166</v>
+        <v>768223</v>
       </c>
       <c r="R10" t="n">
-        <v>7244249</v>
+        <v>7244174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1544,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1563,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831873</v>
+        <v>125831885</v>
       </c>
       <c r="B11" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768223</v>
+        <v>768166</v>
       </c>
       <c r="R11" t="n">
-        <v>7244174</v>
+        <v>7244249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1642,6 +1641,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831886</v>
+        <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768160</v>
+        <v>768152</v>
       </c>
       <c r="R15" t="n">
-        <v>7244178</v>
+        <v>7244247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,7 +2048,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831902</v>
+        <v>125831886</v>
       </c>
       <c r="B16" t="n">
         <v>78977</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768129</v>
+        <v>768160</v>
       </c>
       <c r="R16" t="n">
-        <v>7244186</v>
+        <v>7244178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831852</v>
+        <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768152</v>
+        <v>768129</v>
       </c>
       <c r="R17" t="n">
-        <v>7244247</v>
+        <v>7244186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3053,49 +3053,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831861</v>
+        <v>125831851</v>
       </c>
       <c r="B26" t="n">
-        <v>56848</v>
+        <v>79009</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768249</v>
+        <v>768168</v>
       </c>
       <c r="R26" t="n">
-        <v>7244155</v>
+        <v>7244250</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,11 +3124,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3159,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831895</v>
+        <v>125831879</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>91256</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3170,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3194,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768193</v>
+        <v>768140</v>
       </c>
       <c r="R27" t="n">
-        <v>7244227</v>
+        <v>7243836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3256,10 +3247,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831851</v>
+        <v>125831895</v>
       </c>
       <c r="B28" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3258,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3282,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768168</v>
+        <v>768193</v>
       </c>
       <c r="R28" t="n">
-        <v>7244250</v>
+        <v>7244227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3353,45 +3344,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831879</v>
+        <v>125831861</v>
       </c>
       <c r="B29" t="n">
-        <v>91256</v>
+        <v>56848</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768140</v>
+        <v>768249</v>
       </c>
       <c r="R29" t="n">
-        <v>7243836</v>
+        <v>7244155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,6 +3419,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831880</v>
+        <v>125831881</v>
       </c>
       <c r="B30" t="n">
-        <v>91403</v>
+        <v>91260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768186</v>
+        <v>768188</v>
       </c>
       <c r="R30" t="n">
-        <v>7244183</v>
+        <v>7244214</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,32 +3644,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831881</v>
+        <v>125831880</v>
       </c>
       <c r="B32" t="n">
-        <v>91260</v>
+        <v>91403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768188</v>
+        <v>768186</v>
       </c>
       <c r="R32" t="n">
-        <v>7244214</v>
+        <v>7244183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125831901</v>
+        <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768103</v>
+        <v>768188</v>
       </c>
       <c r="R37" t="n">
-        <v>7244200</v>
+        <v>7244204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4226,10 +4226,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125831874</v>
+        <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768188</v>
+        <v>768103</v>
       </c>
       <c r="R38" t="n">
-        <v>7244204</v>
+        <v>7244200</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,10 +4429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125831894</v>
+        <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4440,21 +4440,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768196</v>
+        <v>768184</v>
       </c>
       <c r="R40" t="n">
-        <v>7244226</v>
+        <v>7244205</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125831850</v>
+        <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4537,21 +4537,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>768184</v>
+        <v>768196</v>
       </c>
       <c r="R41" t="n">
-        <v>7244205</v>
+        <v>7244226</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125831892</v>
+        <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4634,21 +4634,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>768218</v>
+        <v>768211</v>
       </c>
       <c r="R42" t="n">
-        <v>7244142</v>
+        <v>7244074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125831893</v>
+        <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>768199</v>
+        <v>768124</v>
       </c>
       <c r="R43" t="n">
-        <v>7244222</v>
+        <v>7244210</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125831855</v>
+        <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>768211</v>
+        <v>768218</v>
       </c>
       <c r="R44" t="n">
-        <v>7244074</v>
+        <v>7244142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125831854</v>
+        <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>768124</v>
+        <v>768199</v>
       </c>
       <c r="R45" t="n">
-        <v>7244210</v>
+        <v>7244222</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831853</v>
+        <v>125831888</v>
       </c>
       <c r="B3" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768115</v>
+        <v>768148</v>
       </c>
       <c r="R3" t="n">
-        <v>7244249</v>
+        <v>7243853</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831888</v>
+        <v>125831896</v>
       </c>
       <c r="B4" t="n">
         <v>78977</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768148</v>
+        <v>768175</v>
       </c>
       <c r="R4" t="n">
-        <v>7243853</v>
+        <v>7244238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831896</v>
+        <v>125831853</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768175</v>
+        <v>768115</v>
       </c>
       <c r="R5" t="n">
-        <v>7244238</v>
+        <v>7244249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831873</v>
+        <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768223</v>
+        <v>768166</v>
       </c>
       <c r="R10" t="n">
-        <v>7244174</v>
+        <v>7244249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,6 +1544,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1562,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831885</v>
+        <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768166</v>
+        <v>768107</v>
       </c>
       <c r="R11" t="n">
-        <v>7244249</v>
+        <v>7244257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,7 +1642,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831866</v>
+        <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>57816</v>
+        <v>92724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768107</v>
+        <v>768223</v>
       </c>
       <c r="R12" t="n">
-        <v>7244257</v>
+        <v>7244174</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2850,49 +2850,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831862</v>
+        <v>125831878</v>
       </c>
       <c r="B24" t="n">
-        <v>56848</v>
+        <v>58297</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>103042</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768217</v>
+        <v>768177</v>
       </c>
       <c r="R24" t="n">
-        <v>7244177</v>
+        <v>7244173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2921,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,45 +2947,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831878</v>
+        <v>125831862</v>
       </c>
       <c r="B25" t="n">
-        <v>58297</v>
+        <v>56848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103042</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768177</v>
+        <v>768217</v>
       </c>
       <c r="R25" t="n">
-        <v>7244173</v>
+        <v>7244177</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831888</v>
+        <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768148</v>
+        <v>768115</v>
       </c>
       <c r="R3" t="n">
-        <v>7243853</v>
+        <v>7244249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831896</v>
+        <v>125831876</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>5479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768175</v>
+        <v>768216</v>
       </c>
       <c r="R4" t="n">
-        <v>7244238</v>
+        <v>7244197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831853</v>
+        <v>125831888</v>
       </c>
       <c r="B5" t="n">
-        <v>79009</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768115</v>
+        <v>768148</v>
       </c>
       <c r="R5" t="n">
-        <v>7244249</v>
+        <v>7243853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831876</v>
+        <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>5479</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768216</v>
+        <v>768175</v>
       </c>
       <c r="R6" t="n">
-        <v>7244197</v>
+        <v>7244238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1143,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831871</v>
+        <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>79001</v>
+        <v>91210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768129</v>
+        <v>768096</v>
       </c>
       <c r="R13" t="n">
-        <v>7244186</v>
+        <v>7243909</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831857</v>
+        <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>91207</v>
+        <v>79004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768096</v>
+        <v>768129</v>
       </c>
       <c r="R14" t="n">
-        <v>7243909</v>
+        <v>7244186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
         <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125831900</v>
+        <v>125831890</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>768138</v>
+        <v>768204</v>
       </c>
       <c r="R19" t="n">
-        <v>7244250</v>
+        <v>7243995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125831890</v>
+        <v>125831882</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,16 +2478,23 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>768204</v>
+        <v>768173</v>
       </c>
       <c r="R20" t="n">
-        <v>7243995</v>
+        <v>7244085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2522,12 +2529,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2546,10 +2559,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125831882</v>
+        <v>125831900</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,23 +2588,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>768173</v>
+        <v>768138</v>
       </c>
       <c r="R21" t="n">
-        <v>7244085</v>
+        <v>7244250</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2626,18 +2632,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>125831899</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>125831878</v>
       </c>
       <c r="B24" t="n">
-        <v>58297</v>
+        <v>58300</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>125831862</v>
       </c>
       <c r="B25" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125831851</v>
+        <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79009</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768168</v>
+        <v>768193</v>
       </c>
       <c r="R26" t="n">
-        <v>7244250</v>
+        <v>7244227</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,45 +3150,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831879</v>
+        <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>91256</v>
+        <v>56849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768140</v>
+        <v>768249</v>
       </c>
       <c r="R27" t="n">
-        <v>7243836</v>
+        <v>7244155</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,6 +3225,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3247,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831895</v>
+        <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>79012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3258,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3282,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768193</v>
+        <v>768168</v>
       </c>
       <c r="R28" t="n">
-        <v>7244227</v>
+        <v>7244250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,49 +3353,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831861</v>
+        <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>56848</v>
+        <v>91259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768249</v>
+        <v>768140</v>
       </c>
       <c r="R29" t="n">
-        <v>7244155</v>
+        <v>7243836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,11 +3424,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831881</v>
+        <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91260</v>
+        <v>91406</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768188</v>
+        <v>768186</v>
       </c>
       <c r="R30" t="n">
-        <v>7244214</v>
+        <v>7244183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831889</v>
+        <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>91263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768182</v>
+        <v>768188</v>
       </c>
       <c r="R31" t="n">
-        <v>7243990</v>
+        <v>7244214</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,32 +3644,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831880</v>
+        <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>91403</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768186</v>
+        <v>768182</v>
       </c>
       <c r="R32" t="n">
-        <v>7244183</v>
+        <v>7243990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3744,7 +3744,7 @@
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>125831860</v>
       </c>
       <c r="B39" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -2850,45 +2850,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831878</v>
+        <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>58300</v>
+        <v>56849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103042</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768177</v>
+        <v>768217</v>
       </c>
       <c r="R24" t="n">
-        <v>7244173</v>
+        <v>7244177</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2921,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2947,49 +2956,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831862</v>
+        <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>56849</v>
+        <v>58300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>103042</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768217</v>
+        <v>768177</v>
       </c>
       <c r="R25" t="n">
-        <v>7244177</v>
+        <v>7244173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91210</v>
+        <v>91295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>79012</v>
+        <v>79050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>125831876</v>
       </c>
       <c r="B4" t="n">
-        <v>5479</v>
+        <v>5480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,6 +906,15 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
@@ -963,14 +980,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>125831888</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,14 +1081,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,14 +1182,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,14 +1283,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,14 +1397,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,6 +1434,14 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
@@ -1461,14 +1506,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,14 +1608,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,6 +1645,14 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
@@ -1656,14 +1717,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92727</v>
+        <v>92813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,14 +1818,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91210</v>
+        <v>91295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,14 +1919,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>79004</v>
+        <v>79042</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,14 +2020,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>79012</v>
+        <v>79050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,14 +2121,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,14 +2222,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,14 +2323,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,14 +2437,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>125831890</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,14 +2538,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>125831882</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,14 +2652,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>125831900</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,14 +2753,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,14 +2854,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>125831899</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,14 +2955,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2881,7 +2994,11 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2952,14 +3069,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>58300</v>
+        <v>58304</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,14 +3170,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3146,14 +3271,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,7 +3310,11 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3252,14 +3385,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>79012</v>
+        <v>79050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3349,14 +3486,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91259</v>
+        <v>91344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3446,14 +3587,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91406</v>
+        <v>91491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3543,14 +3688,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91263</v>
+        <v>91348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3640,14 +3789,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,14 +3890,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3834,14 +3991,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3931,14 +4092,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3964,6 +4129,14 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
@@ -4028,14 +4201,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4061,6 +4238,14 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
@@ -4125,14 +4310,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92727</v>
+        <v>92813</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4222,14 +4411,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4319,14 +4512,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>125831860</v>
       </c>
       <c r="B39" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,7 +4551,11 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4425,14 +4626,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79012</v>
+        <v>79050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4522,14 +4727,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4619,14 +4828,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79012</v>
+        <v>79050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4716,14 +4929,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79012</v>
+        <v>79050</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4813,14 +5030,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4910,14 +5131,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,7 +5232,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>125831888</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125831890</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>125831900</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>125831899</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>58304</v>
+        <v>58306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91491</v>
+        <v>91493</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125831860</v>
       </c>
       <c r="B39" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91493</v>
+        <v>91499</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>125831888</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125831890</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>125831900</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>125831899</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>58306</v>
+        <v>58309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125831860</v>
       </c>
       <c r="B39" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>125831888</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125831890</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>125831900</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>125831899</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>58309</v>
+        <v>58315</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91502</v>
+        <v>91510</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125831860</v>
       </c>
       <c r="B39" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91510</v>
+        <v>91511</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>125831888</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>79053</v>
+        <v>79056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125831890</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>125831900</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>125831899</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>58315</v>
+        <v>58316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91366</v>
+        <v>91374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91513</v>
+        <v>91521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125831856</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125831853</v>
       </c>
       <c r="B3" t="n">
-        <v>79064</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>125831888</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>125831896</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>125831897</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>125831883</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125831867</v>
       </c>
       <c r="B9" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125831885</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>125831866</v>
       </c>
       <c r="B11" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>125831873</v>
       </c>
       <c r="B12" t="n">
-        <v>92843</v>
+        <v>92854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>91336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>125831871</v>
       </c>
       <c r="B14" t="n">
-        <v>79056</v>
+        <v>79067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>125831852</v>
       </c>
       <c r="B15" t="n">
-        <v>79064</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>125831886</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>125831902</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>125831863</v>
       </c>
       <c r="B18" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125831890</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>125831882</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>125831900</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>125831899</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>125831862</v>
       </c>
       <c r="B24" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>125831878</v>
       </c>
       <c r="B25" t="n">
-        <v>58316</v>
+        <v>58327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>125831861</v>
       </c>
       <c r="B27" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>125831851</v>
       </c>
       <c r="B28" t="n">
-        <v>79064</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125831879</v>
       </c>
       <c r="B29" t="n">
-        <v>91374</v>
+        <v>91385</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125831880</v>
       </c>
       <c r="B30" t="n">
-        <v>91521</v>
+        <v>91532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>125831881</v>
       </c>
       <c r="B31" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>125831889</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>125831898</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>125831887</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>125831868</v>
       </c>
       <c r="B35" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>125831864</v>
       </c>
       <c r="B36" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125831874</v>
       </c>
       <c r="B37" t="n">
-        <v>92843</v>
+        <v>92854</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>125831901</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125831860</v>
       </c>
       <c r="B39" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125831850</v>
       </c>
       <c r="B40" t="n">
-        <v>79064</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>125831894</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>125831855</v>
       </c>
       <c r="B42" t="n">
-        <v>79064</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>125831854</v>
       </c>
       <c r="B43" t="n">
-        <v>79064</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>125831892</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>125831893</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125831856</v>
+        <v>125831850</v>
       </c>
       <c r="B2" t="n">
-        <v>91336</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768162</v>
+        <v>768184</v>
       </c>
       <c r="R2" t="n">
-        <v>7244169</v>
+        <v>7244205</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831853</v>
+        <v>125831851</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768115</v>
+        <v>768168</v>
       </c>
       <c r="R3" t="n">
-        <v>7244249</v>
+        <v>7244250</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,54 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831876</v>
+        <v>125831852</v>
       </c>
       <c r="B4" t="n">
-        <v>5480</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101920</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768216</v>
+        <v>768152</v>
       </c>
       <c r="R4" t="n">
-        <v>7244197</v>
+        <v>7244247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,9 +954,8 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -988,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831888</v>
+        <v>125831853</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768148</v>
+        <v>768115</v>
       </c>
       <c r="R5" t="n">
-        <v>7243853</v>
+        <v>7244249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831896</v>
+        <v>125831854</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768175</v>
+        <v>768124</v>
       </c>
       <c r="R6" t="n">
-        <v>7244238</v>
+        <v>7244210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831897</v>
+        <v>125831855</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768187</v>
+        <v>768211</v>
       </c>
       <c r="R7" t="n">
-        <v>7244255</v>
+        <v>7244074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,52 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831883</v>
+        <v>125831879</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768238</v>
+        <v>768140</v>
       </c>
       <c r="R8" t="n">
-        <v>7244188</v>
+        <v>7243836</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,18 +1354,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,53 +1382,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831867</v>
+        <v>125831880</v>
       </c>
       <c r="B9" t="n">
-        <v>57681</v>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768108</v>
+        <v>768186</v>
       </c>
       <c r="R9" t="n">
-        <v>7243943</v>
+        <v>7244183</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831885</v>
+        <v>125831873</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768166</v>
+        <v>768223</v>
       </c>
       <c r="R10" t="n">
-        <v>7244249</v>
+        <v>7244174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1562,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1616,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831866</v>
+        <v>125831874</v>
       </c>
       <c r="B11" t="n">
-        <v>57844</v>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1627,42 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768107</v>
+        <v>768188</v>
       </c>
       <c r="R11" t="n">
-        <v>7244257</v>
+        <v>7244204</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831873</v>
+        <v>125831856</v>
       </c>
       <c r="B12" t="n">
-        <v>92854</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768223</v>
+        <v>768162</v>
       </c>
       <c r="R12" t="n">
-        <v>7244174</v>
+        <v>7244169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1789,7 @@
         <v>125831857</v>
       </c>
       <c r="B13" t="n">
-        <v>91336</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,45 +1887,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831871</v>
+        <v>125831882</v>
       </c>
       <c r="B14" t="n">
-        <v>79067</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768129</v>
+        <v>768173</v>
       </c>
       <c r="R14" t="n">
-        <v>7244186</v>
+        <v>7244085</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,12 +1967,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2028,45 +2001,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831852</v>
+        <v>125831883</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768152</v>
+        <v>768238</v>
       </c>
       <c r="R15" t="n">
-        <v>7244247</v>
+        <v>7244188</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,12 +2081,18 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2129,14 +2115,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125831886</v>
+        <v>125831885</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2164,10 +2150,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768160</v>
+        <v>768166</v>
       </c>
       <c r="R16" t="n">
-        <v>7244178</v>
+        <v>7244249</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,6 +2194,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2230,14 +2217,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125831902</v>
+        <v>125831886</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2265,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768129</v>
+        <v>768160</v>
       </c>
       <c r="R17" t="n">
-        <v>7244186</v>
+        <v>7244178</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,53 +2318,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125831863</v>
+        <v>125831887</v>
       </c>
       <c r="B18" t="n">
-        <v>57844</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768181</v>
+        <v>768147</v>
       </c>
       <c r="R18" t="n">
-        <v>7244196</v>
+        <v>7244072</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,11 +2389,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,14 +2419,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125831890</v>
+        <v>125831888</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2480,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>768204</v>
+        <v>768148</v>
       </c>
       <c r="R19" t="n">
-        <v>7243995</v>
+        <v>7243853</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,14 +2520,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125831882</v>
+        <v>125831889</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2575,23 +2549,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>768173</v>
+        <v>768182</v>
       </c>
       <c r="R20" t="n">
-        <v>7244085</v>
+        <v>7243990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,18 +2593,12 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2660,14 +2621,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125831900</v>
+        <v>125831890</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2695,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>768138</v>
+        <v>768204</v>
       </c>
       <c r="R21" t="n">
-        <v>7244250</v>
+        <v>7243995</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,11 +2725,11 @@
         <v>125831891</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2862,14 +2823,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125831899</v>
+        <v>125831892</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2897,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768171</v>
+        <v>768218</v>
       </c>
       <c r="R23" t="n">
-        <v>7244251</v>
+        <v>7244142</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,53 +2924,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125831862</v>
+        <v>125831893</v>
       </c>
       <c r="B24" t="n">
-        <v>56875</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768217</v>
+        <v>768199</v>
       </c>
       <c r="R24" t="n">
-        <v>7244177</v>
+        <v>7244222</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,11 +2995,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3077,32 +3025,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125831878</v>
+        <v>125831894</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103042</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3112,10 +3060,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768177</v>
+        <v>768196</v>
       </c>
       <c r="R25" t="n">
-        <v>7244173</v>
+        <v>7244226</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,11 +3129,11 @@
         <v>125831895</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3279,53 +3227,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125831861</v>
+        <v>125831896</v>
       </c>
       <c r="B27" t="n">
-        <v>56875</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768249</v>
+        <v>768175</v>
       </c>
       <c r="R27" t="n">
-        <v>7244155</v>
+        <v>7244238</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,11 +3298,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3393,32 +3328,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125831851</v>
+        <v>125831897</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3428,10 +3363,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768168</v>
+        <v>768187</v>
       </c>
       <c r="R28" t="n">
-        <v>7244250</v>
+        <v>7244255</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3494,32 +3429,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125831879</v>
+        <v>125831898</v>
       </c>
       <c r="B29" t="n">
-        <v>91385</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3529,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768140</v>
+        <v>768185</v>
       </c>
       <c r="R29" t="n">
-        <v>7243836</v>
+        <v>7244244</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3595,10 +3530,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125831880</v>
+        <v>125831899</v>
       </c>
       <c r="B30" t="n">
-        <v>91532</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3606,21 +3541,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3630,10 +3565,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768186</v>
+        <v>768171</v>
       </c>
       <c r="R30" t="n">
-        <v>7244183</v>
+        <v>7244251</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3696,32 +3631,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125831881</v>
+        <v>125831900</v>
       </c>
       <c r="B31" t="n">
-        <v>91389</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3731,10 +3666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768188</v>
+        <v>768138</v>
       </c>
       <c r="R31" t="n">
-        <v>7244214</v>
+        <v>7244250</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3797,14 +3732,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125831889</v>
+        <v>125831901</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3832,10 +3767,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768182</v>
+        <v>768103</v>
       </c>
       <c r="R32" t="n">
-        <v>7243990</v>
+        <v>7244200</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,14 +3833,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125831898</v>
+        <v>125831902</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3933,10 +3868,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>768185</v>
+        <v>768129</v>
       </c>
       <c r="R33" t="n">
-        <v>7244244</v>
+        <v>7244186</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3999,32 +3934,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125831887</v>
+        <v>125831871</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4034,10 +3969,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768147</v>
+        <v>768129</v>
       </c>
       <c r="R34" t="n">
-        <v>7244072</v>
+        <v>7244186</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4100,14 +4035,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125831868</v>
+        <v>125831867</v>
       </c>
       <c r="B35" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4143,10 +4078,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768122</v>
+        <v>768108</v>
       </c>
       <c r="R35" t="n">
-        <v>7243923</v>
+        <v>7243943</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4209,32 +4144,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125831864</v>
+        <v>125831868</v>
       </c>
       <c r="B36" t="n">
-        <v>57844</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4252,10 +4187,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768102</v>
+        <v>768122</v>
       </c>
       <c r="R36" t="n">
-        <v>7244258</v>
+        <v>7243923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4318,45 +4253,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125831874</v>
+        <v>125831860</v>
       </c>
       <c r="B37" t="n">
-        <v>92854</v>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768188</v>
+        <v>768101</v>
       </c>
       <c r="R37" t="n">
-        <v>7244204</v>
+        <v>7243942</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4389,6 +4332,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4419,45 +4367,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125831901</v>
+        <v>125831861</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768103</v>
+        <v>768249</v>
       </c>
       <c r="R38" t="n">
-        <v>7244200</v>
+        <v>7244155</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4490,6 +4446,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4520,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125831860</v>
+        <v>125831862</v>
       </c>
       <c r="B39" t="n">
-        <v>56875</v>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4563,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>768101</v>
+        <v>768217</v>
       </c>
       <c r="R39" t="n">
-        <v>7243942</v>
+        <v>7244177</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4603,7 +4564,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4634,45 +4595,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125831850</v>
+        <v>125831876</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>5482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>101920</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768184</v>
+        <v>768216</v>
       </c>
       <c r="R40" t="n">
-        <v>7244205</v>
+        <v>7244197</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4711,8 +4681,9 @@
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4735,10 +4706,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125831894</v>
+        <v>125831863</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4746,34 +4717,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>768196</v>
+        <v>768181</v>
       </c>
       <c r="R41" t="n">
-        <v>7244226</v>
+        <v>7244196</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4806,6 +4785,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4836,10 +4820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125831855</v>
+        <v>125831864</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,34 +4831,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>768211</v>
+        <v>768102</v>
       </c>
       <c r="R42" t="n">
-        <v>7244074</v>
+        <v>7244258</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4937,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125831854</v>
+        <v>125831866</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4948,34 +4940,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norr om storslyet, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>768124</v>
+        <v>768107</v>
       </c>
       <c r="R43" t="n">
-        <v>7244210</v>
+        <v>7244257</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5038,32 +5038,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125831892</v>
+        <v>125831878</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>58602</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103042</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>768218</v>
+        <v>768177</v>
       </c>
       <c r="R44" t="n">
-        <v>7244142</v>
+        <v>7244173</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5132,107 +5132,6 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>125831893</v>
-      </c>
-      <c r="B45" t="n">
-        <v>79043</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Norr om storslyet, Vb</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>768199</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7244222</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Byske</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 48290-2024 artfynd.xlsx
+++ b/artfynd/A 48290-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831879</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831857</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831888</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831889</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831890</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831867</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831868</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831860</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831850</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831851</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1812,6 +1867,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831852</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1913,6 +1973,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831853</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831854</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831855</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2216,6 +2291,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831880</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2317,6 +2397,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831873</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2418,6 +2503,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831874</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831856</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2633,6 +2728,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831882</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2747,6 +2847,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831883</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2849,6 +2954,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831885</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2950,6 +3060,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831886</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3051,6 +3166,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831887</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3152,6 +3272,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831891</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3253,6 +3378,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831892</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3354,6 +3484,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831893</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3455,6 +3590,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831894</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3556,6 +3696,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831895</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3657,6 +3802,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831896</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3758,6 +3908,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831897</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3859,6 +4014,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831898</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3960,6 +4120,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831899</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4061,6 +4226,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831900</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4162,6 +4332,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831901</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4263,6 +4438,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831902</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4364,6 +4544,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831871</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4478,6 +4663,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831861</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4590,6 +4780,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831862</t>
         </is>
       </c>
     </row>
@@ -4703,6 +4898,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831876</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4817,6 +5017,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831863</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4926,6 +5131,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831864</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5035,6 +5245,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831866</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5136,8 +5351,58 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831878</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>